--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484048_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484048_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6142</v>
+        <v>5.7134</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6581</v>
+        <v>5.4767</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0439</v>
+        <v>0.2366</v>
       </c>
       <c r="G2" t="n">
         <v>0.09229999999999999</v>
@@ -610,13 +610,13 @@
         <v>2.579</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1928</v>
+        <v>0.2919</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5839</v>
+        <v>0.4026</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3912</v>
+        <v>-0.1106</v>
       </c>
       <c r="V2" t="n">
         <v>2.7502</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.259</v>
+        <v>4.1312</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2785</v>
+        <v>3.4032</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9805</v>
+        <v>0.728</v>
       </c>
       <c r="G3" t="n">
         <v>0.7751</v>
@@ -688,13 +688,13 @@
         <v>2.9758</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2714</v>
+        <v>1.1435</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6463</v>
+        <v>0.771</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6251</v>
+        <v>0.3726</v>
       </c>
       <c r="V3" t="n">
         <v>1.2207</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4861</v>
+        <v>3.3898</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7152</v>
+        <v>5.3104</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.2291</v>
+        <v>-1.9205</v>
       </c>
       <c r="G4" t="n">
         <v>-0.3178</v>
@@ -766,13 +766,13 @@
         <v>2.579</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6784</v>
+        <v>0.2253</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2946</v>
+        <v>0.3005</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3838</v>
+        <v>-0.0752</v>
       </c>
       <c r="V4" t="n">
         <v>1.8952</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8749</v>
+        <v>2.798</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0802</v>
+        <v>2.9191</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2053</v>
+        <v>-0.1211</v>
       </c>
       <c r="G5" t="n">
         <v>0.0285</v>
@@ -844,13 +844,13 @@
         <v>2.579</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9472</v>
+        <v>-0.0241</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7368</v>
+        <v>0.1021</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2104</v>
+        <v>-0.1262</v>
       </c>
       <c r="V5" t="n">
         <v>1.2065</v>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2819</v>
+        <v>0.6146</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2239</v>
+        <v>-0.0596</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5058</v>
+        <v>0.6742</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2498</v>
@@ -918,13 +918,13 @@
         <v>0.9919</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4602</v>
+        <v>-0.1275</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4251</v>
+        <v>-0.2607</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0352</v>
+        <v>0.1332</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -951,13 +951,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2819</v>
+        <v>0.6146</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2239</v>
+        <v>-0.0596</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5058</v>
+        <v>0.6742</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2498</v>
@@ -996,13 +996,13 @@
         <v>0.9919</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4602</v>
+        <v>-0.1275</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4251</v>
+        <v>-0.2607</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0352</v>
+        <v>0.1332</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1017,7 +1017,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. GASSAMA KARGBO</t>
+          <t>G. RODRIGUEZ FLAQUE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1029,73 +1029,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2799</v>
+        <v>-0.505</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1672</v>
+        <v>-0.2528</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4471</v>
+        <v>-0.2522</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-1.7831</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0049</v>
+        <v>0.1511</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-1.9343</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5729</v>
+        <v>-0.5192</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3279</v>
+        <v>0.0806</v>
       </c>
       <c r="L8" t="n">
-        <v>1.245</v>
+        <v>-0.5999</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6672</v>
+        <v>-1.2639</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3328</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="O8" t="n">
         <v>-1.3344</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.3806</v>
+        <v>0.9919</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="S8" t="n">
-        <v>2.066</v>
+        <v>0.2863</v>
       </c>
       <c r="T8" t="n">
-        <v>1.2357</v>
+        <v>0.2664</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8303</v>
+        <v>0.0198</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6888</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6888</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>,. VICENTE SABARIEGO</t>
+          <t>P. MULIO CAMPOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1107,73 +1107,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7426</v>
+        <v>-0.7844</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1791</v>
+        <v>-0.4739</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4364</v>
+        <v>-0.3106</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4531</v>
+        <v>-1.1847</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4531</v>
+        <v>-0.6651</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-0.5195</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4531</v>
+        <v>-0.0649</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4531</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-1.1197</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-0.5951</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9919</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.5952</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4364</v>
+        <v>-0.4237</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4364</v>
+        <v>0.1997</v>
       </c>
       <c r="V9" t="n">
-        <v>0.266</v>
+        <v>1.2207</v>
       </c>
       <c r="W9" t="n">
-        <v>0.266</v>
+        <v>1.2065</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.0143</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. MULIO CAMPOS</t>
+          <t>B. GASSAMA KARGBO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1185,73 +1185,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.825</v>
+        <v>-0.8551</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5985</v>
+        <v>-0.8814</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2264</v>
+        <v>0.0262</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1847</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6651</v>
+        <v>-0.0049</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5195</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0649</v>
+        <v>1.5729</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.3279</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0051</v>
+        <v>1.245</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1197</v>
+        <v>-1.6672</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5951</v>
+        <v>-0.3328</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-1.3344</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3968</v>
+        <v>-2.3806</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R10" t="n">
         <v>0.5952</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4642</v>
+        <v>0.931</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7481</v>
+        <v>0.5215</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2839</v>
+        <v>0.4095</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2207</v>
+        <v>0.6888</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0143</v>
+        <v>0.6888</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ FLAQUE</t>
+          <t>,. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1263,64 +1263,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8672</v>
+        <v>-0.9297</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5589</v>
+        <v>-1.1791</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3083</v>
+        <v>0.2494</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.7831</v>
+        <v>-0.4531</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1511</v>
+        <v>-0.4531</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.9343</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5192</v>
+        <v>-0.4531</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0806</v>
+        <v>-0.4531</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5999</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2639</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0.07049999999999999</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3344</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9919</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9919</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0759</v>
+        <v>0.2494</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0396</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0363</v>
+        <v>0.2494</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1341,13 +1341,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2857</v>
+        <v>-1.5957</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5055</v>
+        <v>-1.6472</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2198</v>
+        <v>0.0515</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1512</v>
@@ -1386,13 +1386,13 @@
         <v>1.1903</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6076</v>
+        <v>0.2976</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1928</v>
+        <v>0.0511</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4148</v>
+        <v>0.2465</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9405</v>
@@ -1407,7 +1407,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. CRUZ URBANEJA</t>
+          <t>P. SAIZ FUENTES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1419,73 +1419,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.8546</v>
+        <v>-1.7747</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5907</v>
+        <v>-0.6846</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.4454</v>
+        <v>-1.0901</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.223</v>
+        <v>-1.2084</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5998</v>
+        <v>-0.3831</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8227</v>
+        <v>-0.8253</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5656</v>
+        <v>0.313</v>
       </c>
       <c r="K13" t="n">
-        <v>1.5981</v>
+        <v>0.348</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.0325</v>
+        <v>-0.0351</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.7885</v>
+        <v>-1.5213</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9983</v>
+        <v>-0.7311</v>
       </c>
       <c r="O13" t="n">
         <v>-0.7902</v>
       </c>
       <c r="P13" t="n">
+        <v>-0.1984</v>
+      </c>
+      <c r="Q13" t="n">
         <v>-0.9919</v>
       </c>
-      <c r="Q13" t="n">
-        <v>-1.9838</v>
-      </c>
       <c r="R13" t="n">
-        <v>0.9919</v>
+        <v>0.7935</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8327</v>
+        <v>0.221</v>
       </c>
       <c r="T13" t="n">
-        <v>1.009</v>
+        <v>-0.0056</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1763</v>
+        <v>0.2267</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.4724</v>
+        <v>-0.589</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.4724</v>
+        <v>-0.589</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. SAIZ FUENTES</t>
+          <t>A. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1497,67 +1497,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.3675</v>
+        <v>-2.3203</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.053</v>
+        <v>0.0409</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3145</v>
+        <v>-2.3612</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.2084</v>
+        <v>-0.223</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3831</v>
+        <v>0.5998</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8253</v>
+        <v>-0.8227</v>
       </c>
       <c r="J14" t="n">
-        <v>0.313</v>
+        <v>1.5656</v>
       </c>
       <c r="K14" t="n">
-        <v>0.348</v>
+        <v>1.5981</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0351</v>
+        <v>-0.0325</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5213</v>
+        <v>-1.7885</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7311</v>
+        <v>-0.9983</v>
       </c>
       <c r="O14" t="n">
         <v>-0.7902</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1984</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3718</v>
+        <v>0.367</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3741</v>
+        <v>0.4592</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0022</v>
+        <v>-0.0922</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.589</v>
+        <v>-1.4724</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.589</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="15">
@@ -1575,13 +1575,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.135300000000003</v>
+        <v>8.496700000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>10.8127</v>
+        <v>11.9121</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.677499999999999</v>
+        <v>-3.4156</v>
       </c>
       <c r="G15" t="n">
         <v>-6.0193</v>
@@ -1590,7 +1590,7 @@
         <v>-6.4249</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4055000000000005</v>
+        <v>0.4055000000000006</v>
       </c>
       <c r="J15" t="n">
         <v>12.8998</v>
@@ -1605,13 +1605,13 @@
         <v>-18.9189</v>
       </c>
       <c r="N15" t="n">
-        <v>-8.6784</v>
+        <v>-8.678399999999998</v>
       </c>
       <c r="O15" t="n">
         <v>-10.2405</v>
       </c>
       <c r="P15" t="n">
-        <v>4.959600000000001</v>
+        <v>4.9596</v>
       </c>
       <c r="Q15" t="n">
         <v>-12.8948</v>
@@ -1620,16 +1620,16 @@
         <v>17.8546</v>
       </c>
       <c r="S15" t="n">
-        <v>1.949</v>
+        <v>3.3102</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6242999999999999</v>
+        <v>1.7239</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3243</v>
+        <v>1.5864</v>
       </c>
       <c r="V15" t="n">
-        <v>6.2462</v>
+        <v>6.246199999999998</v>
       </c>
       <c r="W15" t="n">
         <v>10.1839</v>
@@ -1653,13 +1653,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.9764</v>
+        <v>5.8274</v>
       </c>
       <c r="E16" t="n">
-        <v>6.7302</v>
+        <v>6.8322</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7539</v>
+        <v>-1.0048</v>
       </c>
       <c r="G16" t="n">
         <v>5.5814</v>
@@ -1698,13 +1698,13 @@
         <v>1.7855</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1841</v>
+        <v>-0.333</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0057</v>
+        <v>0.1078</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.1898</v>
+        <v>-0.4408</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2065</v>
@@ -1731,13 +1731,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1392</v>
+        <v>1.9217</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9272</v>
+        <v>1.3353</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2121</v>
+        <v>0.5864</v>
       </c>
       <c r="G17" t="n">
         <v>2.4416</v>
@@ -1776,13 +1776,13 @@
         <v>1.1903</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3479</v>
+        <v>0.1303</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5611</v>
+        <v>-0.153</v>
       </c>
       <c r="U17" t="n">
-        <v>0.909</v>
+        <v>0.2833</v>
       </c>
       <c r="V17" t="n">
         <v>1.1352</v>
@@ -1809,13 +1809,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7232</v>
+        <v>1.7077</v>
       </c>
       <c r="E18" t="n">
-        <v>1.261</v>
+        <v>1.6691</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5377999999999999</v>
+        <v>0.0387</v>
       </c>
       <c r="G18" t="n">
         <v>1.5519</v>
@@ -1854,13 +1854,13 @@
         <v>1.7855</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6222</v>
+        <v>-0.6377</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9862</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6361</v>
+        <v>-0.0596</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1887,13 +1887,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6022</v>
+        <v>1.0647</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4832</v>
+        <v>1.5852</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.881</v>
+        <v>-0.5205</v>
       </c>
       <c r="G19" t="n">
         <v>1.5806</v>
@@ -1932,13 +1932,13 @@
         <v>1.5871</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5816</v>
+        <v>-0.1191</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1928</v>
+        <v>0.2948</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7743</v>
+        <v>-0.4139</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1953,7 +1953,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. POYATOS PARRA</t>
+          <t>J. RIERA MESTRE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1965,73 +1965,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4615</v>
+        <v>-0.18</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7773</v>
+        <v>0.3953</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3158</v>
+        <v>-0.5753</v>
       </c>
       <c r="G20" t="n">
-        <v>1.6385</v>
+        <v>-0.3245</v>
       </c>
       <c r="H20" t="n">
-        <v>2.2681</v>
+        <v>-1.0785</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6296</v>
+        <v>0.754</v>
       </c>
       <c r="J20" t="n">
-        <v>3.291</v>
+        <v>0.605</v>
       </c>
       <c r="K20" t="n">
-        <v>3.1303</v>
+        <v>-0.6802</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1606</v>
+        <v>1.2852</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6525</v>
+        <v>-0.9295</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8623</v>
+        <v>-0.3983</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7902</v>
+        <v>-0.5312</v>
       </c>
       <c r="P20" t="n">
         <v>0.3968</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3887</v>
+        <v>0.3968</v>
       </c>
       <c r="S20" t="n">
-        <v>1.319</v>
+        <v>-0.2522</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5613</v>
+        <v>-0.2097</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7577</v>
+        <v>-0.0425</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.8927</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-1.083</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.8097</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. RIERA MESTRE</t>
+          <t>C. POYATOS PARRA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2043,73 +2043,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6102</v>
+        <v>-0.3232</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2933</v>
+        <v>1.1651</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9034</v>
+        <v>-1.4883</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3245</v>
+        <v>1.6385</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0785</v>
+        <v>2.2681</v>
       </c>
       <c r="I21" t="n">
-        <v>0.754</v>
+        <v>-0.6296</v>
       </c>
       <c r="J21" t="n">
-        <v>0.605</v>
+        <v>3.291</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6802</v>
+        <v>3.1303</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2852</v>
+        <v>0.1606</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9295</v>
+        <v>-1.6525</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3983</v>
+        <v>-0.8623</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5312</v>
+        <v>-0.7902</v>
       </c>
       <c r="P21" t="n">
         <v>0.3968</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3968</v>
+        <v>1.3887</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6824</v>
+        <v>0.5342</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3117</v>
+        <v>-0.0509</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3707</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-2.8927</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-1.083</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. FLUXA PAYERAS</t>
+          <t>L. SANCHEZ MORENO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2121,73 +2121,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4532</v>
+        <v>-0.7201</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4204</v>
+        <v>0.6397</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0328</v>
+        <v>-1.3597</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1823</v>
+        <v>-2.0351</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5743</v>
+        <v>0.7154</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-2.7505</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0079</v>
+        <v>-1.0053</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9678</v>
+        <v>0.8319</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0402</v>
+        <v>-1.8372</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1902</v>
+        <v>-1.0298</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3935</v>
+        <v>-0.1165</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7967</v>
+        <v>-0.9133</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3968</v>
+        <v>1.9838</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5952</v>
+        <v>1.9838</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.271</v>
+        <v>-0.3316</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4364</v>
+        <v>-0.4307</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1655</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6032</v>
+        <v>-0.3373</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.0757</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6032</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. SANCHEZ MORENO</t>
+          <t>P. FLUXA PAYERAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2199,73 +2199,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.555</v>
+        <v>-1.2815</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3336</v>
+        <v>-0.2164</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8885</v>
+        <v>-1.0651</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.0351</v>
+        <v>-0.1823</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7154</v>
+        <v>0.5743</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.7505</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.0053</v>
+        <v>1.0079</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8319</v>
+        <v>0.9678</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.8372</v>
+        <v>0.0402</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0298</v>
+        <v>-1.1902</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1165</v>
+        <v>-0.3935</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9133</v>
+        <v>-0.7967</v>
       </c>
       <c r="P23" t="n">
-        <v>1.9838</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9838</v>
+        <v>0.5952</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1665</v>
+        <v>-0.0992</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7368</v>
+        <v>-0.2324</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4297</v>
+        <v>0.1332</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3373</v>
+        <v>-0.6032</v>
       </c>
       <c r="W23" t="n">
-        <v>2.0757</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.4129</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. AGUILO RODRIGUEZ</t>
+          <t>M. OCHOGAVIA CIFRE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2277,73 +2277,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2643</v>
+        <v>-3.0014</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1163</v>
+        <v>-2.5063</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.148</v>
+        <v>-0.4951</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.4709</v>
+        <v>-2.4294</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6651</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8058</v>
+        <v>-2.5251</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.2346</v>
+        <v>-1.0327</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.3551</v>
+        <v>0.2876</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1205</v>
+        <v>-1.3202</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2363</v>
+        <v>-1.3967</v>
       </c>
       <c r="N24" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.1918</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9263</v>
+        <v>-1.2048</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.3887</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5952</v>
+        <v>0.7935</v>
       </c>
       <c r="S24" t="n">
-        <v>1.671</v>
+        <v>-0.1077</v>
       </c>
       <c r="T24" t="n">
-        <v>1.2924</v>
+        <v>-0.4817</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3786</v>
+        <v>0.3741</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.0757</v>
+        <v>-0.266</v>
       </c>
       <c r="W24" t="n">
-        <v>1.8097</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.8854</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. OCHOGAVIA CIFRE</t>
+          <t>M. AGUILO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2355,67 +2355,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.3415</v>
+        <v>-4.3628</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.7104</v>
+        <v>-1.2386</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6311</v>
+        <v>-3.1242</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.4294</v>
+        <v>-1.4709</v>
       </c>
       <c r="H25" t="n">
-        <v>0.09569999999999999</v>
+        <v>-0.6651</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.5251</v>
+        <v>-0.8058</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.0327</v>
+        <v>-1.2346</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2876</v>
+        <v>-1.3551</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.3202</v>
+        <v>0.1205</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.3967</v>
+        <v>-0.2363</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1918</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.2048</v>
+        <v>-0.9263</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.1984</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R25" t="n">
-        <v>0.7935</v>
+        <v>0.5952</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4478</v>
+        <v>0.5725</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6858</v>
+        <v>0.1701</v>
       </c>
       <c r="U25" t="n">
-        <v>0.238</v>
+        <v>0.4024</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.266</v>
+        <v>-2.0757</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.8097</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.266</v>
+        <v>-3.8854</v>
       </c>
     </row>
     <row r="26">
@@ -2433,13 +2433,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.5318</v>
+        <v>-5.4655</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.3753</v>
+        <v>-5.4773</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1565</v>
+        <v>0.0118</v>
       </c>
       <c r="G26" t="n">
         <v>-0.5824</v>
@@ -2478,13 +2478,13 @@
         <v>0.7935</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2086</v>
+        <v>0.2749</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3061</v>
+        <v>0.2041</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0975</v>
+        <v>0.0708</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2511,13 +2511,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-6.853499999999999</v>
+        <v>-4.813</v>
       </c>
       <c r="E27" t="n">
-        <v>4.1834</v>
+        <v>4.183300000000003</v>
       </c>
       <c r="F27" t="n">
-        <v>-11.0367</v>
+        <v>-8.9961</v>
       </c>
       <c r="G27" t="n">
         <v>5.769400000000001</v>
@@ -2526,7 +2526,7 @@
         <v>6.4496</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.680400000000001</v>
+        <v>-0.6804000000000009</v>
       </c>
       <c r="J27" t="n">
         <v>18.4682</v>
@@ -2556,13 +2556,13 @@
         <v>12.8951</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.4091</v>
+        <v>-0.3686</v>
       </c>
       <c r="T27" t="n">
         <v>-1.3597</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.0493</v>
+        <v>0.9913000000000001</v>
       </c>
       <c r="V27" t="n">
         <v>-6.2462</v>
